--- a/administrative_forms/029_document_management_system_access_form--administrative_forms.xlsx
+++ b/administrative_forms/029_document_management_system_access_form--administrative_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>User department</t>
+          <t>Department</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>User job position</t>
+          <t>Job position</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -738,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Access start date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Access end date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Assigned tool</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -870,13 +870,13 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Form ID</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Form ID</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assigned tool</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1148,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>admin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Admin</t>
         </is>
       </c>
     </row>
@@ -1165,29 +1004,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>User</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>access_level_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>moderator</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Moderator</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1055,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>access_level_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
